--- a/public/downloads/HansenFirst2018.xlsx
+++ b/public/downloads/HansenFirst2018.xlsx
@@ -1587,16 +1587,16 @@
         <v>22</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.8915959482240874</v>
+        <v>-0.8909160212275538</v>
       </c>
       <c r="O3" s="5">
         <v>99</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8257458905760425</v>
+        <v>0.8257339620322437</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.7032105889147644</v>
+        <v>0.7032395219784467</v>
       </c>
       <c r="R3" s="5">
         <v>94</v>
@@ -1646,16 +1646,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.5720799166148538</v>
+        <v>-0.7105326749965428</v>
       </c>
       <c r="O4" s="5">
         <v>48</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3685712217615765</v>
+        <v>0.3484886203151809</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3413005566977493</v>
+        <v>0.3195444051308208</v>
       </c>
       <c r="R4" s="5">
         <v>48</v>
@@ -1705,7 +1705,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1745691406714778</v>
+        <v>-0.1745691406684422</v>
       </c>
       <c r="O5" s="5">
         <v>36</v>
@@ -1764,16 +1764,16 @@
         <v>1</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.09568535930880692</v>
+        <v>-0.3793203491508166</v>
       </c>
       <c r="O6" s="5">
         <v>36</v>
       </c>
       <c r="P6" s="4">
-        <v>0.5880828539461127</v>
+        <v>0.5105215925351855</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.3627806271331931</v>
+        <v>0.2438879227762656</v>
       </c>
       <c r="R6" s="5">
         <v>35</v>
@@ -1823,16 +1823,16 @@
         <v>2</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.721967652549863</v>
+        <v>-1.683904763554565</v>
       </c>
       <c r="O7" s="5">
         <v>20</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2532710393928146</v>
+        <v>0.2506336665245815</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2217391022341018</v>
+        <v>0.2188379920790453</v>
       </c>
       <c r="R7" s="5">
         <v>20</v>
@@ -1882,16 +1882,16 @@
         <v>7</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.896095564389221</v>
+        <v>-1.867708986953762</v>
       </c>
       <c r="O8" s="5">
         <v>21</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1906406437747543</v>
+        <v>0.1874333647778733</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1906406437747543</v>
+        <v>0.1874333647778733</v>
       </c>
       <c r="R8" s="5">
         <v>21</v>
@@ -1941,16 +1941,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-1.124874735036821</v>
+        <v>-1.137037296438486</v>
       </c>
       <c r="O9" s="5">
         <v>19</v>
       </c>
       <c r="P9" s="4">
-        <v>0.1786824013411642</v>
+        <v>0.177208341587485</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1786824013411642</v>
+        <v>0.177208341587485</v>
       </c>
       <c r="R9" s="5">
         <v>19</v>
@@ -2000,16 +2000,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.2876025861988367</v>
+        <v>-0.2954437658893596</v>
       </c>
       <c r="O10" s="5">
         <v>15</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1588358381938657</v>
+        <v>0.1574521006014205</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1580427740088169</v>
+        <v>0.1575200286961153</v>
       </c>
       <c r="R10" s="5">
         <v>15</v>
@@ -2059,16 +2059,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.6145846729971041</v>
+        <v>-0.6131908887940511</v>
       </c>
       <c r="O11" s="5">
         <v>17</v>
       </c>
       <c r="P11" s="4">
-        <v>0.09638297356920426</v>
+        <v>0.09630098626314233</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.09638297356920426</v>
+        <v>0.09630098626314233</v>
       </c>
       <c r="R11" s="5">
         <v>17</v>
@@ -2118,16 +2118,16 @@
         <v>8</v>
       </c>
       <c r="N12" s="4">
-        <v>-1.861968336586127</v>
+        <v>-2.077135378755855</v>
       </c>
       <c r="O12" s="5">
         <v>14</v>
       </c>
       <c r="P12" s="4">
-        <v>0.7010228958755913</v>
+        <v>0.6829769264997364</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.7390951139566825</v>
+        <v>0.7037333769784604</v>
       </c>
       <c r="R12" s="5">
         <v>14</v>
@@ -2177,16 +2177,16 @@
         <v>1</v>
       </c>
       <c r="N13" s="4">
-        <v>-1.605413539496454</v>
+        <v>-1.682093364872856</v>
       </c>
       <c r="O13" s="5">
         <v>17</v>
       </c>
       <c r="P13" s="4">
-        <v>0.2347792981246561</v>
+        <v>0.2192371814834573</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.2347792981246561</v>
+        <v>0.2192371814834573</v>
       </c>
       <c r="R13" s="5">
         <v>17</v>
@@ -2236,7 +2236,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.8805571478879415</v>
+        <v>-0.8902066176124492</v>
       </c>
       <c r="O14" s="5">
         <v>15</v>
@@ -2245,7 +2245,7 @@
         <v>0.1213839306899684</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1196157595046714</v>
+        <v>0.1189724615230375</v>
       </c>
       <c r="R14" s="5">
         <v>15</v>
@@ -2295,16 +2295,16 @@
         <v>4</v>
       </c>
       <c r="N15" s="4">
-        <v>-1.697288299998982</v>
+        <v>-1.72111324295588</v>
       </c>
       <c r="O15" s="5">
         <v>13</v>
       </c>
       <c r="P15" s="4">
-        <v>0.4523741112418775</v>
+        <v>0.4505414233221162</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.4523741112418775</v>
+        <v>0.4505414233221162</v>
       </c>
       <c r="R15" s="5">
         <v>13</v>
@@ -2477,22 +2477,22 @@
         <v>29</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.967091209694458</v>
+        <v>-1.505327268969268</v>
       </c>
       <c r="O3" s="5">
         <v>69</v>
       </c>
       <c r="P3" s="4">
-        <v>1.532527082935816</v>
+        <v>1.471463868628984</v>
       </c>
       <c r="Q3" s="4">
-        <v>1.189186590360043</v>
+        <v>0.9351387358220368</v>
       </c>
       <c r="R3" s="5">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="S3" s="5">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -2536,16 +2536,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4495853103684827</v>
+        <v>-0.3641831516943057</v>
       </c>
       <c r="O4" s="5">
         <v>42</v>
       </c>
       <c r="P4" s="4">
-        <v>0.7229192688496718</v>
+        <v>0.7260397437988174</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6316149856021891</v>
+        <v>0.6293237227078728</v>
       </c>
       <c r="R4" s="5">
         <v>41</v>
@@ -2595,7 +2595,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.7165873023777749</v>
+        <v>0.7165886136790505</v>
       </c>
       <c r="O5" s="5">
         <v>32</v>
@@ -2654,16 +2654,16 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.1235992016489476</v>
+        <v>-0.4926823826972395</v>
       </c>
       <c r="O6" s="5">
         <v>33</v>
       </c>
       <c r="P6" s="4">
-        <v>0.8078118310395604</v>
+        <v>0.6991370103347435</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.5270748316136918</v>
+        <v>0.422566983708924</v>
       </c>
       <c r="R6" s="5">
         <v>31</v>
@@ -2713,16 +2713,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.5644308443416693</v>
+        <v>-0.4907009636517614</v>
       </c>
       <c r="O7" s="5">
         <v>11</v>
       </c>
       <c r="P7" s="4">
-        <v>0.8552863209420327</v>
+        <v>0.8858316057303455</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.5394963721224214</v>
+        <v>0.5312131145950513</v>
       </c>
       <c r="R7" s="5">
         <v>11</v>
@@ -2772,16 +2772,16 @@
         <v>1</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.073470502026612</v>
+        <v>-1.273822554416256</v>
       </c>
       <c r="O8" s="5">
         <v>15</v>
       </c>
       <c r="P8" s="4">
-        <v>0.4786173896536986</v>
+        <v>0.5003589580966425</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.5420427701218674</v>
+        <v>0.5042209360127647</v>
       </c>
       <c r="R8" s="5">
         <v>15</v>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.1143269133486013</v>
+        <v>0.01434617876657285</v>
       </c>
       <c r="O9" s="5">
         <v>19</v>
       </c>
       <c r="P9" s="4">
-        <v>0.6879907634874827</v>
+        <v>0.6812184954814209</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.6879907634874827</v>
+        <v>0.6812184954814209</v>
       </c>
       <c r="R9" s="5">
         <v>19</v>
@@ -2890,16 +2890,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.8242077223349042</v>
+        <v>0.6984981296991464</v>
       </c>
       <c r="O10" s="5">
         <v>12</v>
       </c>
       <c r="P10" s="4">
-        <v>0.5920796589946216</v>
+        <v>0.5539087952364592</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.4573049345948069</v>
+        <v>0.4519873078491703</v>
       </c>
       <c r="R10" s="5">
         <v>12</v>
@@ -2949,13 +2949,13 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.3958675266912905</v>
+        <v>-0.4734341383882565</v>
       </c>
       <c r="O11" s="5">
         <v>16</v>
       </c>
       <c r="P11" s="4">
-        <v>0.2294042668620344</v>
+        <v>0.224841524997507</v>
       </c>
       <c r="Q11" s="4">
         <v>0.2373141505249805</v>
@@ -3008,13 +3008,13 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.2938617415036008</v>
+        <v>-0.3084791882283753</v>
       </c>
       <c r="O12" s="5">
         <v>14</v>
       </c>
       <c r="P12" s="4">
-        <v>0.7092922363250992</v>
+        <v>0.7101520861324389</v>
       </c>
       <c r="Q12" s="4">
         <v>0.7386658274813921</v>
@@ -3067,16 +3067,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.4757416749395334</v>
+        <v>-0.28568961127894</v>
       </c>
       <c r="O13" s="5">
         <v>17</v>
       </c>
       <c r="P13" s="4">
-        <v>0.7105936029559173</v>
+        <v>0.6994140697994119</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.7105936029559173</v>
+        <v>0.6994140697994119</v>
       </c>
       <c r="R13" s="5">
         <v>17</v>
@@ -3126,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.1230572289011131</v>
+        <v>0.199608645751141</v>
       </c>
       <c r="O14" s="5">
         <v>15</v>
@@ -3135,7 +3135,7 @@
         <v>0.374708144269789</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.3906278022151026</v>
+        <v>0.3855243744251008</v>
       </c>
       <c r="R14" s="5">
         <v>15</v>
@@ -3185,13 +3185,13 @@
         <v>3</v>
       </c>
       <c r="N15" s="4">
-        <v>1.513074753354886</v>
+        <v>1.58860619024199</v>
       </c>
       <c r="O15" s="5">
         <v>8</v>
       </c>
       <c r="P15" s="4">
-        <v>0.9516916282804092</v>
+        <v>0.9691219598697409</v>
       </c>
       <c r="Q15" s="4">
         <v>0.8118836753201322</v>
@@ -3367,16 +3367,16 @@
         <v>3</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.09218521433324156</v>
+        <v>-0.01928251220704169</v>
       </c>
       <c r="O3" s="5">
         <v>93</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7823619309783779</v>
+        <v>0.7748719342017566</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5465346933152969</v>
+        <v>0.5435276042539056</v>
       </c>
       <c r="R3" s="5">
         <v>90</v>
@@ -3426,16 +3426,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1797374600565688</v>
+        <v>0.1682636771061112</v>
       </c>
       <c r="O4" s="5">
         <v>50</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1696125659698752</v>
+        <v>0.1684161897708421</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1444415867958538</v>
+        <v>0.1436563068668777</v>
       </c>
       <c r="R4" s="5">
         <v>50</v>
@@ -3485,7 +3485,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2236640114664546</v>
+        <v>0.2236653753006976</v>
       </c>
       <c r="O5" s="5">
         <v>36</v>
@@ -3544,16 +3544,16 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>0.1684355201697986</v>
+        <v>-0.1984931887513994</v>
       </c>
       <c r="O6" s="5">
         <v>34</v>
       </c>
       <c r="P6" s="4">
-        <v>0.6678085923468677</v>
+        <v>0.5461747840735276</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.4255325023449774</v>
+        <v>0.239167480951756</v>
       </c>
       <c r="R6" s="5">
         <v>32</v>
@@ -3603,16 +3603,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.4534966372121653</v>
+        <v>0.4386322178381477</v>
       </c>
       <c r="O7" s="5">
         <v>21</v>
       </c>
       <c r="P7" s="4">
-        <v>0.214247069298102</v>
+        <v>0.2128957584459185</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1889956674258096</v>
+        <v>0.1882878379318087</v>
       </c>
       <c r="R7" s="5">
         <v>21</v>
@@ -3662,16 +3662,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.4056061411322323</v>
+        <v>0.4134237910694196</v>
       </c>
       <c r="O8" s="5">
         <v>21</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2196510330481815</v>
+        <v>0.2192787640035535</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2196510330481815</v>
+        <v>0.2192787640035535</v>
       </c>
       <c r="R8" s="5">
         <v>21</v>
@@ -3721,16 +3721,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.131085024094976</v>
+        <v>0.05632087254258522</v>
       </c>
       <c r="O9" s="5">
         <v>19</v>
       </c>
       <c r="P9" s="4">
-        <v>0.4143671936871607</v>
+        <v>0.410432238342298</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.4143671936871607</v>
+        <v>0.410432238342298</v>
       </c>
       <c r="R9" s="5">
         <v>19</v>
@@ -3780,16 +3780,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.3593027006889594</v>
+        <v>0.3002225802795575</v>
       </c>
       <c r="O10" s="5">
         <v>15</v>
       </c>
       <c r="P10" s="4">
-        <v>0.276752322506288</v>
+        <v>0.2663264189046289</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.2566142784003717</v>
+        <v>0.2526756037064116</v>
       </c>
       <c r="R10" s="5">
         <v>15</v>
@@ -3839,16 +3839,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>0.04883766905606023</v>
+        <v>0.04028020995917814</v>
       </c>
       <c r="O11" s="5">
         <v>17</v>
       </c>
       <c r="P11" s="4">
-        <v>0.1214021666794968</v>
+        <v>0.1208987867326213</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1214021666794968</v>
+        <v>0.1208987867326213</v>
       </c>
       <c r="R11" s="5">
         <v>17</v>
@@ -3898,16 +3898,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>0.6222734947376409</v>
+        <v>0.6730997366569511</v>
       </c>
       <c r="O12" s="5">
         <v>16</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2981799354647508</v>
+        <v>0.2972953645490377</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.2741044231918686</v>
+        <v>0.2699879264739664</v>
       </c>
       <c r="R12" s="5">
         <v>16</v>
@@ -3957,16 +3957,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.5340199859491752</v>
+        <v>0.4935271708228015</v>
       </c>
       <c r="O13" s="5">
         <v>17</v>
       </c>
       <c r="P13" s="4">
-        <v>0.4148693859137945</v>
+        <v>0.4124874556122431</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.4148693859137945</v>
+        <v>0.4124874556122431</v>
       </c>
       <c r="R13" s="5">
         <v>17</v>
@@ -4016,16 +4016,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.359646550566282</v>
+        <v>0.3727644246639343</v>
       </c>
       <c r="O14" s="5">
         <v>16</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1952904446301389</v>
+        <v>0.1938294818278123</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1952904446301389</v>
+        <v>0.1938294818278123</v>
       </c>
       <c r="R14" s="5">
         <v>16</v>
@@ -4075,16 +4075,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>1.057430740190843</v>
+        <v>1.056136037752793</v>
       </c>
       <c r="O15" s="5">
         <v>13</v>
       </c>
       <c r="P15" s="4">
-        <v>0.4550157189065069</v>
+        <v>0.4549161264112722</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.4550157189065069</v>
+        <v>0.4549161264112722</v>
       </c>
       <c r="R15" s="5">
         <v>13</v>
@@ -4257,22 +4257,22 @@
         <v>10</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.581852180109881</v>
+        <v>-0.4822600274928845</v>
       </c>
       <c r="O3" s="5">
         <v>81</v>
       </c>
       <c r="P3" s="4">
-        <v>0.962232591615731</v>
+        <v>0.9505723684245216</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.7137819192831849</v>
+        <v>0.6932407950439047</v>
       </c>
       <c r="R3" s="5">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="S3" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -4316,16 +4316,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>0.0222981797466603</v>
+        <v>0.06330799584611668</v>
       </c>
       <c r="O4" s="5">
         <v>52</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5441747787986034</v>
+        <v>0.5405539462793129</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5133672350316025</v>
+        <v>0.5104795198374132</v>
       </c>
       <c r="R4" s="5">
         <v>51</v>
@@ -4375,7 +4375,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3496978176539415</v>
+        <v>0.3496960374650371</v>
       </c>
       <c r="O5" s="5">
         <v>30</v>
@@ -4434,16 +4434,16 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.4215150429667524</v>
+        <v>-0.6898981749400264</v>
       </c>
       <c r="O6" s="5">
         <v>36</v>
       </c>
       <c r="P6" s="4">
-        <v>0.8191273962652204</v>
+        <v>0.7841444880188646</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.5887102741106309</v>
+        <v>0.5257255390885153</v>
       </c>
       <c r="R6" s="5">
         <v>35</v>
@@ -4493,16 +4493,16 @@
         <v>2</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.2825898652746608</v>
+        <v>-0.4963801281119231</v>
       </c>
       <c r="O7" s="5">
         <v>21</v>
       </c>
       <c r="P7" s="4">
-        <v>0.7596106955599397</v>
+        <v>0.7511670395774259</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.5506173287363175</v>
+        <v>0.5070841066243654</v>
       </c>
       <c r="R7" s="5">
         <v>19</v>
@@ -4552,13 +4552,13 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.6337390079759644</v>
+        <v>-0.6672747845732374</v>
       </c>
       <c r="O8" s="5">
         <v>20</v>
       </c>
       <c r="P8" s="4">
-        <v>0.310021389720177</v>
+        <v>0.3116183314629043</v>
       </c>
       <c r="Q8" s="4">
         <v>0.2991535134453443</v>
@@ -4611,16 +4611,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.3376321940716783</v>
+        <v>-0.2278965288860491</v>
       </c>
       <c r="O9" s="5">
         <v>18</v>
       </c>
       <c r="P9" s="4">
-        <v>0.3307812152173331</v>
+        <v>0.330462506151219</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.3204642258631927</v>
+        <v>0.314031384894204</v>
       </c>
       <c r="R9" s="5">
         <v>18</v>
@@ -4670,16 +4670,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.3178500859430642</v>
+        <v>0.283426040186896</v>
       </c>
       <c r="O10" s="5">
         <v>15</v>
       </c>
       <c r="P10" s="4">
-        <v>0.2335141541034853</v>
+        <v>0.2246592348665752</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.2427154887225091</v>
+        <v>0.2372697863548335</v>
       </c>
       <c r="R10" s="5">
         <v>15</v>
@@ -4729,16 +4729,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.4171432531702521</v>
+        <v>-0.3790248692093883</v>
       </c>
       <c r="O11" s="5">
         <v>16</v>
       </c>
       <c r="P11" s="4">
-        <v>0.1248634528893115</v>
+        <v>0.1162775055178345</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1149870006158835</v>
+        <v>0.1082468305312432</v>
       </c>
       <c r="R11" s="5">
         <v>16</v>
@@ -4788,16 +4788,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>0.001605224378769943</v>
+        <v>-0.09130238290526904</v>
       </c>
       <c r="O12" s="5">
         <v>17</v>
       </c>
       <c r="P12" s="4">
-        <v>0.6977151137946664</v>
+        <v>0.688050233241109</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.6977151137946664</v>
+        <v>0.688050233241109</v>
       </c>
       <c r="R12" s="5">
         <v>17</v>
@@ -4847,16 +4847,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.02242879877394444</v>
+        <v>0.132881358920713</v>
       </c>
       <c r="O13" s="5">
         <v>16</v>
       </c>
       <c r="P13" s="4">
-        <v>0.4099152984277038</v>
+        <v>0.4024575650897425</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.402257639523782</v>
+        <v>0.384626912996282</v>
       </c>
       <c r="R13" s="5">
         <v>16</v>
@@ -4906,16 +4906,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.1787507367582293</v>
+        <v>0.1740385654557031</v>
       </c>
       <c r="O14" s="5">
         <v>15</v>
       </c>
       <c r="P14" s="4">
-        <v>0.2203023151809248</v>
+        <v>0.219713293768109</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.2153837914551453</v>
+        <v>0.2150696467016436</v>
       </c>
       <c r="R14" s="5">
         <v>15</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>0.7771720919533566</v>
+        <v>0.8181018281902652</v>
       </c>
       <c r="O15" s="5">
         <v>7</v>
       </c>
       <c r="P15" s="4">
-        <v>0.4071530711214739</v>
+        <v>0.3911196718444654</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.4205349846184729</v>
+        <v>0.4146878794417717</v>
       </c>
       <c r="R15" s="5">
         <v>7</v>
@@ -5147,16 +5147,16 @@
         <v>6</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4325976806314126</v>
+        <v>-0.3259720492278575</v>
       </c>
       <c r="O3" s="5">
         <v>96</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7792440146884565</v>
+        <v>0.7713452147129972</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6724791066117228</v>
+        <v>0.667012335799502</v>
       </c>
       <c r="R3" s="5">
         <v>91</v>
@@ -5206,16 +5206,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.06576575943806044</v>
+        <v>0.1016201743768761</v>
       </c>
       <c r="O4" s="5">
         <v>48</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2846167018159669</v>
+        <v>0.2825406776908214</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.261973510012985</v>
+        <v>0.2597244838774107</v>
       </c>
       <c r="R4" s="5">
         <v>48</v>
@@ -5265,7 +5265,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2334498701108233</v>
+        <v>0.2338560792704811</v>
       </c>
       <c r="O5" s="5">
         <v>34</v>
@@ -5324,16 +5324,16 @@
         <v>1</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.1354233656768754</v>
+        <v>-0.2956136383872945</v>
       </c>
       <c r="O6" s="5">
         <v>35</v>
       </c>
       <c r="P6" s="4">
-        <v>0.5356773409023196</v>
+        <v>0.5087569944425923</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.3657796253609675</v>
+        <v>0.3325971412542619</v>
       </c>
       <c r="R6" s="5">
         <v>34</v>
@@ -5383,16 +5383,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.04429720158874434</v>
+        <v>0.007816981931682676</v>
       </c>
       <c r="O7" s="5">
         <v>21</v>
       </c>
       <c r="P7" s="4">
-        <v>0.5521833906890078</v>
+        <v>0.5515606355766067</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.5151770515195141</v>
+        <v>0.5120430136150735</v>
       </c>
       <c r="R7" s="5">
         <v>21</v>
@@ -5442,16 +5442,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.09235731402683693</v>
+        <v>-0.1087650384870358</v>
       </c>
       <c r="O8" s="5">
         <v>21</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3990735672663763</v>
+        <v>0.3976032935717653</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.3990735672663763</v>
+        <v>0.3976032935717653</v>
       </c>
       <c r="R8" s="5">
         <v>21</v>
@@ -5501,16 +5501,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.3976024423065705</v>
+        <v>-0.2506635099416599</v>
       </c>
       <c r="O9" s="5">
         <v>19</v>
       </c>
       <c r="P9" s="4">
-        <v>0.3689214762786714</v>
+        <v>0.3429499522646534</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.3689214762786714</v>
+        <v>0.3429499522646534</v>
       </c>
       <c r="R9" s="5">
         <v>19</v>
@@ -5560,16 +5560,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.09526158709195442</v>
+        <v>-0.06733615137636662</v>
       </c>
       <c r="O10" s="5">
         <v>15</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1288185074261171</v>
+        <v>0.1260170163312817</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1309630478771093</v>
+        <v>0.1277880246362959</v>
       </c>
       <c r="R10" s="5">
         <v>15</v>
@@ -5619,16 +5619,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.2034156385088863</v>
+        <v>-0.1786927977445885</v>
       </c>
       <c r="O11" s="5">
         <v>16</v>
       </c>
       <c r="P11" s="4">
-        <v>0.1865876993031313</v>
+        <v>0.1852404724593404</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1783692662124849</v>
+        <v>0.1753926601431886</v>
       </c>
       <c r="R11" s="5">
         <v>16</v>
@@ -5678,16 +5678,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.01678660920708139</v>
+        <v>-0.09788638754980639</v>
       </c>
       <c r="O12" s="5">
         <v>17</v>
       </c>
       <c r="P12" s="4">
-        <v>0.5988669007151327</v>
+        <v>0.5940963255185018</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.5988669007151327</v>
+        <v>0.5940963255185018</v>
       </c>
       <c r="R12" s="5">
         <v>17</v>
@@ -5737,16 +5737,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.02118546223380904</v>
+        <v>0.0201264455972705</v>
       </c>
       <c r="O13" s="5">
         <v>17</v>
       </c>
       <c r="P13" s="4">
-        <v>0.3424472920426408</v>
+        <v>0.3400171798172831</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.3424472920426408</v>
+        <v>0.3400171798172831</v>
       </c>
       <c r="R13" s="5">
         <v>17</v>
@@ -5796,7 +5796,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.04354812570181821</v>
+        <v>0.0321389934324543</v>
       </c>
       <c r="O14" s="5">
         <v>16</v>
@@ -5855,16 +5855,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>0.5579208964078973</v>
+        <v>0.3533162571839057</v>
       </c>
       <c r="O15" s="5">
         <v>13</v>
       </c>
       <c r="P15" s="4">
-        <v>0.5787767265866836</v>
+        <v>0.549750471178693</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.5787767265866836</v>
+        <v>0.549750471178693</v>
       </c>
       <c r="R15" s="5">
         <v>13</v>
@@ -6037,22 +6037,22 @@
         <v>30</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.364557469269585</v>
+        <v>-0.8288764037715737</v>
       </c>
       <c r="O3" s="5">
         <v>96</v>
       </c>
       <c r="P3" s="4">
-        <v>1.084106051306942</v>
+        <v>0.9801144178129841</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.9754929208639724</v>
+        <v>0.5170606928163891</v>
       </c>
       <c r="R3" s="5">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="S3" s="5">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -6096,16 +6096,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3523787011520472</v>
+        <v>-0.4370154776588606</v>
       </c>
       <c r="O4" s="5">
         <v>50</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3397546267281722</v>
+        <v>0.3311657124227517</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3307339876585174</v>
+        <v>0.3251869878411526</v>
       </c>
       <c r="R4" s="5">
         <v>50</v>
@@ -6155,13 +6155,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4826112958700024</v>
+        <v>0.4826112958689919</v>
       </c>
       <c r="O5" s="5">
         <v>36</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4218878203196659</v>
+        <v>0.4218878203197164</v>
       </c>
       <c r="Q5" s="4">
         <v>0.4358270723073979</v>
@@ -6214,16 +6214,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.5878764356992277</v>
+        <v>-0.6662738126760814</v>
       </c>
       <c r="O6" s="5">
         <v>37</v>
       </c>
       <c r="P6" s="4">
-        <v>0.4340223090091033</v>
+        <v>0.4238461545148312</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.218711964177062</v>
+        <v>0.2055918680487446</v>
       </c>
       <c r="R6" s="5">
         <v>37</v>
@@ -6273,7 +6273,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.039129886219078</v>
+        <v>-1.062901169498218</v>
       </c>
       <c r="O7" s="5">
         <v>21</v>
@@ -6282,7 +6282,7 @@
         <v>0.2762612305576278</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2726216184357054</v>
+        <v>0.2714896525652702</v>
       </c>
       <c r="R7" s="5">
         <v>21</v>
@@ -6332,16 +6332,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.7531935792274973</v>
+        <v>-0.6492881509766448</v>
       </c>
       <c r="O8" s="5">
         <v>21</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2721457497615107</v>
+        <v>0.2590546667509313</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2721457497615107</v>
+        <v>0.2590546667509313</v>
       </c>
       <c r="R8" s="5">
         <v>21</v>
@@ -6391,16 +6391,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.001257077886533041</v>
+        <v>0.09164244921703357</v>
       </c>
       <c r="O9" s="5">
         <v>19</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2380551792055768</v>
+        <v>0.2245002912026585</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2380551792055768</v>
+        <v>0.2245002912026585</v>
       </c>
       <c r="R9" s="5">
         <v>19</v>
@@ -6450,13 +6450,13 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.2475555395221818</v>
+        <v>0.2547371544060297</v>
       </c>
       <c r="O10" s="5">
         <v>16</v>
       </c>
       <c r="P10" s="4">
-        <v>0.08984132374799254</v>
+        <v>0.08941887581364855</v>
       </c>
       <c r="Q10" s="4">
         <v>0.09409499063895055</v>
@@ -6509,13 +6509,13 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.2684839709809239</v>
+        <v>-0.2694888517871732</v>
       </c>
       <c r="O11" s="5">
         <v>16</v>
       </c>
       <c r="P11" s="4">
-        <v>0.09441626542144042</v>
+        <v>0.0943571547857787</v>
       </c>
       <c r="Q11" s="4">
         <v>0.07528245203047845</v>
@@ -6568,16 +6568,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.2865642899987506</v>
+        <v>-0.4904552960651927</v>
       </c>
       <c r="O12" s="5">
         <v>16</v>
       </c>
       <c r="P12" s="4">
-        <v>0.6316113914852608</v>
+        <v>0.6055252026151934</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.5773255594659759</v>
+        <v>0.5623521716706819</v>
       </c>
       <c r="R12" s="5">
         <v>16</v>
@@ -6627,16 +6627,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.3366095679341336</v>
+        <v>-0.3434788973827381</v>
       </c>
       <c r="O13" s="5">
         <v>17</v>
       </c>
       <c r="P13" s="4">
-        <v>0.2245308319125832</v>
+        <v>0.2241267537097241</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.2245308319125832</v>
+        <v>0.2241267537097241</v>
       </c>
       <c r="R13" s="5">
         <v>17</v>
@@ -6686,7 +6686,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.07408513947836279</v>
+        <v>0.1019542061985703</v>
       </c>
       <c r="O14" s="5">
         <v>15</v>
@@ -6695,7 +6695,7 @@
         <v>0.110217340784402</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1167432185593578</v>
+        <v>0.1148852807780107</v>
       </c>
       <c r="R14" s="5">
         <v>15</v>
@@ -6745,16 +6745,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>0.9140221158785817</v>
+        <v>0.8776926808059216</v>
       </c>
       <c r="O15" s="5">
         <v>13</v>
       </c>
       <c r="P15" s="4">
-        <v>0.349925384158613</v>
+        <v>0.3471308122299469</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.349925384158613</v>
+        <v>0.3471308122299469</v>
       </c>
       <c r="R15" s="5">
         <v>13</v>
@@ -6927,16 +6927,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1420864658348776</v>
+        <v>0.2086149874668308</v>
       </c>
       <c r="O3" s="5">
         <v>105</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2823740934100336</v>
+        <v>0.2769116363267322</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2356905284486601</v>
+        <v>0.2316606756619888</v>
       </c>
       <c r="R3" s="5">
         <v>105</v>
@@ -6986,16 +6986,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2863788167051325</v>
+        <v>0.2957228190862704</v>
       </c>
       <c r="O4" s="5">
         <v>50</v>
       </c>
       <c r="P4" s="4">
-        <v>0.08406084388018574</v>
+        <v>0.0830396898481242</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.07807025398273852</v>
+        <v>0.07738201388464003</v>
       </c>
       <c r="R4" s="5">
         <v>50</v>
@@ -7045,7 +7045,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.07604498421566114</v>
+        <v>0.07604497402280863</v>
       </c>
       <c r="O5" s="5">
         <v>38</v>
@@ -7104,16 +7104,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.06235514467108279</v>
+        <v>-0.06219774461351335</v>
       </c>
       <c r="O6" s="5">
         <v>37</v>
       </c>
       <c r="P6" s="4">
-        <v>0.3180104638905968</v>
+        <v>0.3179947238848399</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1314517277565831</v>
+        <v>0.1314474737009732</v>
       </c>
       <c r="R6" s="5">
         <v>37</v>
@@ -7163,16 +7163,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.7022685568478767</v>
+        <v>0.7237138885248982</v>
       </c>
       <c r="O7" s="5">
         <v>22</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1169318404375399</v>
+        <v>0.1135842677957241</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1169318404375399</v>
+        <v>0.1135842677957241</v>
       </c>
       <c r="R7" s="5">
         <v>22</v>
@@ -7222,16 +7222,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.5223571466867195</v>
+        <v>0.6304090696795583</v>
       </c>
       <c r="O8" s="5">
         <v>21</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2114740917654609</v>
+        <v>0.1849826381963123</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2114740917654609</v>
+        <v>0.1849826381963123</v>
       </c>
       <c r="R8" s="5">
         <v>21</v>
@@ -7281,16 +7281,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.00683202217320618</v>
+        <v>0.1367891666304928</v>
       </c>
       <c r="O9" s="5">
         <v>19</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2666181173462574</v>
+        <v>0.2457626252626785</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2666181173462574</v>
+        <v>0.2457626252626785</v>
       </c>
       <c r="R9" s="5">
         <v>19</v>
@@ -7340,16 +7340,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.02681717514368711</v>
+        <v>0.06272437471488956</v>
       </c>
       <c r="O10" s="5">
         <v>17</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1656632113993939</v>
+        <v>0.1559502162897011</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1656632113993939</v>
+        <v>0.1559502162897011</v>
       </c>
       <c r="R10" s="5">
         <v>17</v>
@@ -7399,16 +7399,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>0.1140040400578258</v>
+        <v>0.1404740542857561</v>
       </c>
       <c r="O11" s="5">
         <v>16</v>
       </c>
       <c r="P11" s="4">
-        <v>0.1157767392467821</v>
+        <v>0.1091841526885057</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.06671446009795937</v>
+        <v>0.05805546099054498</v>
       </c>
       <c r="R11" s="5">
         <v>16</v>
@@ -7458,16 +7458,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>0.5034595844824026</v>
+        <v>0.6376633167674868</v>
       </c>
       <c r="O12" s="5">
         <v>17</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2636905920141425</v>
+        <v>0.2196232802534</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.2636905920141425</v>
+        <v>0.2196232802534</v>
       </c>
       <c r="R12" s="5">
         <v>17</v>
@@ -7517,16 +7517,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.3548990302532995</v>
+        <v>0.5049211403820379</v>
       </c>
       <c r="O13" s="5">
         <v>17</v>
       </c>
       <c r="P13" s="4">
-        <v>0.2787809166003932</v>
+        <v>0.2285388995600683</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.2787809166003932</v>
+        <v>0.2285388995600683</v>
       </c>
       <c r="R13" s="5">
         <v>17</v>
@@ -7576,16 +7576,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.2060640490826815</v>
+        <v>0.2724628857031917</v>
       </c>
       <c r="O14" s="5">
         <v>16</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1320772385977393</v>
+        <v>0.12045364961432</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1320772385977393</v>
+        <v>0.12045364961432</v>
       </c>
       <c r="R14" s="5">
         <v>16</v>
@@ -7635,16 +7635,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>0.3632719061436163</v>
+        <v>0.4857149831950451</v>
       </c>
       <c r="O15" s="5">
         <v>13</v>
       </c>
       <c r="P15" s="4">
-        <v>0.3511233189723402</v>
+        <v>0.3278040848762028</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.3511233189723402</v>
+        <v>0.3278040848762028</v>
       </c>
       <c r="R15" s="5">
         <v>13</v>
@@ -7817,16 +7817,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5225002755214933</v>
+        <v>-0.4620120696490631</v>
       </c>
       <c r="O3" s="5">
         <v>99</v>
       </c>
       <c r="P3" s="4">
-        <v>0.612165448964299</v>
+        <v>0.6098637452800783</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4926203107448656</v>
+        <v>0.4869149041856403</v>
       </c>
       <c r="R3" s="5">
         <v>99</v>
@@ -7876,16 +7876,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.229983522405443</v>
+        <v>-0.2594924151999134</v>
       </c>
       <c r="O4" s="5">
         <v>48</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3984715999352241</v>
+        <v>0.3958584167271182</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2600478020996835</v>
+        <v>0.2596759280237746</v>
       </c>
       <c r="R4" s="5">
         <v>48</v>
@@ -7935,7 +7935,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4004137675367393</v>
+        <v>0.4004134806891528</v>
       </c>
       <c r="O5" s="5">
         <v>32</v>
@@ -7994,16 +7994,16 @@
         <v>1</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.549811536616983</v>
+        <v>-0.6955738598335302</v>
       </c>
       <c r="O6" s="5">
         <v>34</v>
       </c>
       <c r="P6" s="4">
-        <v>0.3418287787346984</v>
+        <v>0.3141619469733989</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1575854528233391</v>
+        <v>0.1192698171088873</v>
       </c>
       <c r="R6" s="5">
         <v>33</v>
@@ -8053,16 +8053,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.3430246742119553</v>
+        <v>-0.4746840058360817</v>
       </c>
       <c r="O7" s="5">
         <v>21</v>
       </c>
       <c r="P7" s="4">
-        <v>0.4071859322304379</v>
+        <v>0.3710046913249944</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.4211382879427732</v>
+        <v>0.3878395399903403</v>
       </c>
       <c r="R7" s="5">
         <v>21</v>
@@ -8112,16 +8112,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.2331546906595131</v>
+        <v>-0.2512524731574786</v>
       </c>
       <c r="O8" s="5">
         <v>21</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3449991156489638</v>
+        <v>0.3441373164823941</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.3449991156489638</v>
+        <v>0.3441373164823941</v>
       </c>
       <c r="R8" s="5">
         <v>21</v>
@@ -8171,16 +8171,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.2343353725652862</v>
+        <v>-0.2458925909014624</v>
       </c>
       <c r="O9" s="5">
         <v>19</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2215528477203746</v>
+        <v>0.2209445730711022</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2215528477203746</v>
+        <v>0.2209445730711022</v>
       </c>
       <c r="R9" s="5">
         <v>19</v>
@@ -8230,16 +8230,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.0353626653136323</v>
+        <v>0.01521775692526717</v>
       </c>
       <c r="O10" s="5">
         <v>16</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1617096133836011</v>
+        <v>0.1610964602081921</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1621347218980881</v>
+        <v>0.1602241898749432</v>
       </c>
       <c r="R10" s="5">
         <v>16</v>
@@ -8289,16 +8289,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.2173871547129242</v>
+        <v>-0.207068298768732</v>
       </c>
       <c r="O11" s="5">
         <v>17</v>
       </c>
       <c r="P11" s="4">
-        <v>0.1122433326330394</v>
+        <v>0.1116363411069105</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1122433326330394</v>
+        <v>0.1116363411069105</v>
       </c>
       <c r="R11" s="5">
         <v>17</v>
@@ -8348,16 +8348,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.1231515886705573</v>
+        <v>-0.1824837207386167</v>
       </c>
       <c r="O12" s="5">
         <v>17</v>
       </c>
       <c r="P12" s="4">
-        <v>0.3243192859624788</v>
+        <v>0.3070277248617493</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.3243192859624788</v>
+        <v>0.3070277248617493</v>
       </c>
       <c r="R12" s="5">
         <v>17</v>
@@ -8407,16 +8407,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.02051482378994799</v>
+        <v>-0.02442445163609364</v>
       </c>
       <c r="O13" s="5">
         <v>17</v>
       </c>
       <c r="P13" s="4">
-        <v>0.3016147451803664</v>
+        <v>0.2989712583905991</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.3016147451803664</v>
+        <v>0.2989712583905991</v>
       </c>
       <c r="R13" s="5">
         <v>17</v>
@@ -8466,16 +8466,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.04099939616661397</v>
+        <v>0.03658937814179808</v>
       </c>
       <c r="O14" s="5">
         <v>16</v>
       </c>
       <c r="P14" s="4">
-        <v>0.08480571235225548</v>
+        <v>0.08455558056358159</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.08480571235225548</v>
+        <v>0.08455558056358159</v>
       </c>
       <c r="R14" s="5">
         <v>16</v>
@@ -8525,16 +8525,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>0.3898726888314151</v>
+        <v>0.252982864563819</v>
       </c>
       <c r="O15" s="5">
         <v>13</v>
       </c>
       <c r="P15" s="4">
-        <v>0.3253160172817756</v>
+        <v>0.2906456095157396</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.3253160172817756</v>
+        <v>0.2906456095157396</v>
       </c>
       <c r="R15" s="5">
         <v>13</v>
@@ -8707,16 +8707,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1695837391315012</v>
+        <v>0.2371517863721238</v>
       </c>
       <c r="O3" s="5">
         <v>102</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2974765812176396</v>
+        <v>0.2886104949436289</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2685487905209781</v>
+        <v>0.2612893626163239</v>
       </c>
       <c r="R3" s="5">
         <v>102</v>
@@ -8766,16 +8766,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2809686400405377</v>
+        <v>0.2978462968603823</v>
       </c>
       <c r="O4" s="5">
         <v>50</v>
       </c>
       <c r="P4" s="4">
-        <v>0.08760308532958197</v>
+        <v>0.08567361438844366</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.08093534195785297</v>
+        <v>0.07960379845186293</v>
       </c>
       <c r="R4" s="5">
         <v>50</v>
@@ -8825,7 +8825,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.0629058411955664</v>
+        <v>0.06290605395406779</v>
       </c>
       <c r="O5" s="5">
         <v>36</v>
@@ -8884,16 +8884,16 @@
         <v>1</v>
       </c>
       <c r="N6" s="4">
-        <v>0.07193763393042141</v>
+        <v>-0.02004455297719687</v>
       </c>
       <c r="O6" s="5">
         <v>37</v>
       </c>
       <c r="P6" s="4">
-        <v>0.3637375525100258</v>
+        <v>0.3494477773838291</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1829550804789974</v>
+        <v>0.1619674310661333</v>
       </c>
       <c r="R6" s="5">
         <v>36</v>
@@ -8943,16 +8943,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.6601796730036033</v>
+        <v>0.6846911390894377</v>
       </c>
       <c r="O7" s="5">
         <v>22</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1279969434377935</v>
+        <v>0.1242585782245045</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1279969434377935</v>
+        <v>0.1242585782245045</v>
       </c>
       <c r="R7" s="5">
         <v>22</v>
@@ -9002,16 +9002,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.4670669954766626</v>
+        <v>0.5487151429989012</v>
       </c>
       <c r="O8" s="5">
         <v>21</v>
       </c>
       <c r="P8" s="4">
-        <v>0.216589300564614</v>
+        <v>0.1926202714967165</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.216589300564614</v>
+        <v>0.1926202714967165</v>
       </c>
       <c r="R8" s="5">
         <v>21</v>
@@ -9061,16 +9061,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.02362843901666616</v>
+        <v>0.06666137010324746</v>
       </c>
       <c r="O9" s="5">
         <v>19</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2883805554206978</v>
+        <v>0.272795952227762</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2883805554206978</v>
+        <v>0.272795952227762</v>
       </c>
       <c r="R9" s="5">
         <v>19</v>
@@ -9120,16 +9120,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.01218019225395071</v>
+        <v>0.06865817168727517</v>
       </c>
       <c r="O10" s="5">
         <v>17</v>
       </c>
       <c r="P10" s="4">
-        <v>0.176554101144664</v>
+        <v>0.1628855663567443</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.176554101144664</v>
+        <v>0.1628855663567443</v>
       </c>
       <c r="R10" s="5">
         <v>17</v>
@@ -9179,16 +9179,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>0.09648778281644949</v>
+        <v>0.1304070830155979</v>
       </c>
       <c r="O11" s="5">
         <v>16</v>
       </c>
       <c r="P11" s="4">
-        <v>0.1197971960192997</v>
+        <v>0.1141871768533626</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.07131698082458007</v>
+        <v>0.0632363791983252</v>
       </c>
       <c r="R11" s="5">
         <v>16</v>
@@ -9238,16 +9238,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>0.4271030665644547</v>
+        <v>0.530708272883146</v>
       </c>
       <c r="O12" s="5">
         <v>17</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2734679494356818</v>
+        <v>0.2319717724244253</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.2734679494356818</v>
+        <v>0.2319717724244253</v>
       </c>
       <c r="R12" s="5">
         <v>17</v>
@@ -9297,16 +9297,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.2990360249797887</v>
+        <v>0.4176447828650041</v>
       </c>
       <c r="O13" s="5">
         <v>17</v>
       </c>
       <c r="P13" s="4">
-        <v>0.3035335678209204</v>
+        <v>0.2744689056562639</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.3035335678209204</v>
+        <v>0.2744689056562639</v>
       </c>
       <c r="R13" s="5">
         <v>17</v>
@@ -9356,16 +9356,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.1663017588880518</v>
+        <v>0.2298723976710235</v>
       </c>
       <c r="O14" s="5">
         <v>16</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1359115996371034</v>
+        <v>0.1210547196160459</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1359115996371034</v>
+        <v>0.1210547196160459</v>
       </c>
       <c r="R14" s="5">
         <v>16</v>
@@ -9415,16 +9415,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>0.3046627277105429</v>
+        <v>0.3761866797285052</v>
       </c>
       <c r="O15" s="5">
         <v>13</v>
       </c>
       <c r="P15" s="4">
-        <v>0.372496330629111</v>
+        <v>0.3465753672667086</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.372496330629111</v>
+        <v>0.3465753672667086</v>
       </c>
       <c r="R15" s="5">
         <v>13</v>
@@ -9597,16 +9597,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.6244862891005459</v>
+        <v>0.703861548245186</v>
       </c>
       <c r="O3" s="5">
         <v>93</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5711782461887853</v>
+        <v>0.5596605941726989</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4150614075065424</v>
+        <v>0.4069174772288932</v>
       </c>
       <c r="R3" s="5">
         <v>93</v>
@@ -9656,16 +9656,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.7117219276578529</v>
+        <v>0.6992866896471313</v>
       </c>
       <c r="O4" s="5">
         <v>46</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2424972717966573</v>
+        <v>0.2415455281621146</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.136338672671826</v>
+        <v>0.1358034510854178</v>
       </c>
       <c r="R4" s="5">
         <v>46</v>
@@ -9715,7 +9715,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1955770583192271</v>
+        <v>0.1955754730006305</v>
       </c>
       <c r="O5" s="5">
         <v>36</v>
@@ -9774,16 +9774,16 @@
         <v>1</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.1866698324854079</v>
+        <v>-0.4442562465992523</v>
       </c>
       <c r="O6" s="5">
         <v>34</v>
       </c>
       <c r="P6" s="4">
-        <v>0.5292611263629682</v>
+        <v>0.420098708774821</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2607625362046793</v>
+        <v>0.138395745981004</v>
       </c>
       <c r="R6" s="5">
         <v>33</v>
@@ -9833,16 +9833,16 @@
         <v>3</v>
       </c>
       <c r="N7" s="4">
-        <v>1.703930610052325</v>
+        <v>1.696762767678429</v>
       </c>
       <c r="O7" s="5">
         <v>20</v>
       </c>
       <c r="P7" s="4">
-        <v>0.5335456384825673</v>
+        <v>0.5331819946864481</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.3270958495396741</v>
+        <v>0.3262975334402783</v>
       </c>
       <c r="R7" s="5">
         <v>19</v>
@@ -9892,16 +9892,16 @@
         <v>1</v>
       </c>
       <c r="N8" s="4">
-        <v>1.274881224482679</v>
+        <v>1.258329916017786</v>
       </c>
       <c r="O8" s="5">
         <v>20</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2829643439832814</v>
+        <v>0.2815893641534493</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2641445140223455</v>
+        <v>0.2635283506242665</v>
       </c>
       <c r="R8" s="5">
         <v>20</v>
@@ -9951,16 +9951,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.1914451308081108</v>
+        <v>0.1698795105330646</v>
       </c>
       <c r="O9" s="5">
         <v>19</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2168919814941936</v>
+        <v>0.2157569488481386</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2168919814941936</v>
+        <v>0.2157569488481386</v>
       </c>
       <c r="R9" s="5">
         <v>19</v>
@@ -10010,16 +10010,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.05518511876716387</v>
+        <v>-0.01957178734301124</v>
       </c>
       <c r="O10" s="5">
         <v>17</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1711356391134546</v>
+        <v>0.1660935780006056</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1711356391134546</v>
+        <v>0.1660935780006056</v>
       </c>
       <c r="R10" s="5">
         <v>17</v>
@@ -10069,13 +10069,13 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>0.2678719806987933</v>
+        <v>0.2780774825368688</v>
       </c>
       <c r="O11" s="5">
         <v>14</v>
       </c>
       <c r="P11" s="4">
-        <v>0.1534894704036135</v>
+        <v>0.155290441316215</v>
       </c>
       <c r="Q11" s="4">
         <v>0.09446195557497765</v>
@@ -10128,16 +10128,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>1.252491701476417</v>
+        <v>1.328338346233096</v>
       </c>
       <c r="O12" s="5">
         <v>14</v>
       </c>
       <c r="P12" s="4">
-        <v>0.3432854264654767</v>
+        <v>0.3525097634919811</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.2250229598760192</v>
+        <v>0.2199710881032004</v>
       </c>
       <c r="R12" s="5">
         <v>14</v>
@@ -10187,16 +10187,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>1.220141560571125</v>
+        <v>1.257393461419326</v>
       </c>
       <c r="O13" s="5">
         <v>17</v>
       </c>
       <c r="P13" s="4">
-        <v>0.2689718170013689</v>
+        <v>0.2654972348596909</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.2689718170013689</v>
+        <v>0.2654972348596909</v>
       </c>
       <c r="R13" s="5">
         <v>17</v>
@@ -10246,16 +10246,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.505787696617507</v>
+        <v>0.512560398325121</v>
       </c>
       <c r="O14" s="5">
         <v>16</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1089687617667287</v>
+        <v>0.1087355528989016</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1089687617667287</v>
+        <v>0.1087355528989016</v>
       </c>
       <c r="R14" s="5">
         <v>16</v>
@@ -10305,16 +10305,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>0.9078724662585125</v>
+        <v>0.7416209147777408</v>
       </c>
       <c r="O15" s="5">
         <v>13</v>
       </c>
       <c r="P15" s="4">
-        <v>0.3328616590822576</v>
+        <v>0.313887314548577</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.3328616590822576</v>
+        <v>0.313887314548577</v>
       </c>
       <c r="R15" s="5">
         <v>13</v>
@@ -10433,13 +10433,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="3">
-        <v>80.24691358024691</v>
+        <v>80.49382716049382</v>
       </c>
       <c r="C3" s="3">
         <v>3.703703703703703</v>
       </c>
       <c r="D3" s="3">
-        <v>16.04938271604938</v>
+        <v>15.80246913580247</v>
       </c>
       <c r="E3" s="3">
         <v>0.4938271604938271</v>
@@ -10448,16 +10448,16 @@
         <v>6.666666666666667</v>
       </c>
       <c r="G3" s="3">
-        <v>8.888888888888889</v>
+        <v>8.641975308641975</v>
       </c>
       <c r="H3" s="4">
-        <v>0.707100533510602</v>
+        <v>0.6565692931998421</v>
       </c>
       <c r="I3" s="4">
-        <v>0.4661284944354184</v>
+        <v>0.3698754569637134</v>
       </c>
       <c r="J3" s="4">
-        <v>0.6889151188718001</v>
+        <v>0.6384230655711431</v>
       </c>
       <c r="K3" s="4">
         <v>85.95590828924173</v>
@@ -10483,13 +10483,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="3">
-        <v>77.03703703703704</v>
+        <v>75.06172839506173</v>
       </c>
       <c r="C4" s="3">
         <v>6.91358024691358</v>
       </c>
       <c r="D4" s="3">
-        <v>16.04938271604938</v>
+        <v>18.02469135802469</v>
       </c>
       <c r="E4" s="3">
         <v>1.481481481481482</v>
@@ -10498,16 +10498,16 @@
         <v>12.59259259259259</v>
       </c>
       <c r="G4" s="3">
-        <v>1.975308641975309</v>
+        <v>3.950617283950617</v>
       </c>
       <c r="H4" s="4">
-        <v>0.6753709306767054</v>
+        <v>0.6593416168952337</v>
       </c>
       <c r="I4" s="4">
-        <v>0.5596331711503502</v>
+        <v>0.4944111449769097</v>
       </c>
       <c r="J4" s="4">
-        <v>0.6766334522906408</v>
+        <v>0.6509628228599602</v>
       </c>
       <c r="K4" s="4">
         <v>76.51003611321053</v>
@@ -10551,13 +10551,13 @@
         <v>0.7407407407407408</v>
       </c>
       <c r="H5" s="4">
-        <v>0.4410557647092171</v>
+        <v>0.4227888717272076</v>
       </c>
       <c r="I5" s="4">
-        <v>0.3557794636068828</v>
+        <v>0.3372139256931645</v>
       </c>
       <c r="J5" s="4">
-        <v>0.4337162644843171</v>
+        <v>0.4082018576443833</v>
       </c>
       <c r="K5" s="4">
         <v>85.90484588897287</v>
@@ -10601,13 +10601,13 @@
         <v>2.716049382716049</v>
       </c>
       <c r="H6" s="4">
-        <v>0.6232410391980222</v>
+        <v>0.605188508197934</v>
       </c>
       <c r="I6" s="4">
-        <v>0.5117137840582724</v>
+        <v>0.4901308657364864</v>
       </c>
       <c r="J6" s="4">
-        <v>0.6332868787964455</v>
+        <v>0.6247970357153531</v>
       </c>
       <c r="K6" s="4">
         <v>80.93667590492994</v>
@@ -10651,13 +10651,13 @@
         <v>0.9876543209876543</v>
       </c>
       <c r="H7" s="4">
-        <v>0.3363866368103015</v>
+        <v>0.3162782455543358</v>
       </c>
       <c r="I7" s="4">
-        <v>0.2868071560309013</v>
+        <v>0.2654028852269912</v>
       </c>
       <c r="J7" s="4">
-        <v>0.345150660979459</v>
+        <v>0.3246691369515359</v>
       </c>
       <c r="K7" s="4">
         <v>88.14680440077269</v>
@@ -10701,13 +10701,13 @@
         <v>1.481481481481482</v>
       </c>
       <c r="H8" s="4">
-        <v>0.5137219644579311</v>
+        <v>0.5015707854171417</v>
       </c>
       <c r="I8" s="4">
-        <v>0.4224195361273755</v>
+        <v>0.4055014259783511</v>
       </c>
       <c r="J8" s="4">
-        <v>0.5015600614800716</v>
+        <v>0.4932071842646884</v>
       </c>
       <c r="K8" s="4">
         <v>85.31855211220271</v>
@@ -10733,13 +10733,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="3">
-        <v>71.11111111111111</v>
+        <v>69.62962962962963</v>
       </c>
       <c r="C9" s="3">
         <v>10.8641975308642</v>
       </c>
       <c r="D9" s="3">
-        <v>18.02469135802469</v>
+        <v>19.50617283950617</v>
       </c>
       <c r="E9" s="3">
         <v>0.4938271604938271</v>
@@ -10748,16 +10748,16 @@
         <v>13.82716049382716</v>
       </c>
       <c r="G9" s="3">
-        <v>3.703703703703703</v>
+        <v>5.185185185185185</v>
       </c>
       <c r="H9" s="4">
-        <v>0.9075589403565185</v>
+        <v>0.8808395575092427</v>
       </c>
       <c r="I9" s="4">
-        <v>0.6829117054421571</v>
+        <v>0.610410618943322</v>
       </c>
       <c r="J9" s="4">
-        <v>0.8967784312096604</v>
+        <v>0.8488579527794363</v>
       </c>
       <c r="K9" s="4">
         <v>77.70496346686814</v>
@@ -10801,13 +10801,13 @@
         <v>1.234567901234568</v>
       </c>
       <c r="H10" s="4">
-        <v>0.4489111777604485</v>
+        <v>0.433701961428721</v>
       </c>
       <c r="I10" s="4">
-        <v>0.3368145355181277</v>
+        <v>0.3187162066839265</v>
       </c>
       <c r="J10" s="4">
-        <v>0.4167853100198226</v>
+        <v>0.4038758267606657</v>
       </c>
       <c r="K10" s="4">
         <v>83.69085411942602</v>
@@ -10833,13 +10833,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="3">
-        <v>82.22222222222221</v>
+        <v>81.9753086419753</v>
       </c>
       <c r="C11" s="3">
         <v>5.432098765432099</v>
       </c>
       <c r="D11" s="3">
-        <v>12.34567901234568</v>
+        <v>12.59259259259259</v>
       </c>
       <c r="E11" s="3">
         <v>0</v>
@@ -10848,16 +10848,16 @@
         <v>9.62962962962963</v>
       </c>
       <c r="G11" s="3">
-        <v>2.716049382716049</v>
+        <v>2.962962962962963</v>
       </c>
       <c r="H11" s="4">
-        <v>0.6070767517708296</v>
+        <v>0.5974950656137087</v>
       </c>
       <c r="I11" s="4">
-        <v>0.4791703174487146</v>
+        <v>0.4619704982083295</v>
       </c>
       <c r="J11" s="4">
-        <v>0.626857474098961</v>
+        <v>0.6213881382514417</v>
       </c>
       <c r="K11" s="4">
         <v>83.49903418157413</v>
@@ -10901,13 +10901,13 @@
         <v>1.481481481481482</v>
       </c>
       <c r="H12" s="4">
-        <v>0.4940254583166888</v>
+        <v>0.4861401574824682</v>
       </c>
       <c r="I12" s="4">
-        <v>0.42517806846747</v>
+        <v>0.4171151198208051</v>
       </c>
       <c r="J12" s="4">
-        <v>0.504759096730481</v>
+        <v>0.4973579105436924</v>
       </c>
       <c r="K12" s="4">
         <v>82.83841437809727</v>
@@ -10933,13 +10933,13 @@
         <v>27</v>
       </c>
       <c r="B13" s="3">
-        <v>90.61728395061729</v>
+        <v>86.41975308641975</v>
       </c>
       <c r="C13" s="3">
         <v>1.975308641975309</v>
       </c>
       <c r="D13" s="3">
-        <v>7.407407407407407</v>
+        <v>11.60493827160494</v>
       </c>
       <c r="E13" s="3">
         <v>0.4938271604938271</v>
@@ -10948,16 +10948,16 @@
         <v>5.432098765432099</v>
       </c>
       <c r="G13" s="3">
-        <v>1.481481481481482</v>
+        <v>5.679012345679013</v>
       </c>
       <c r="H13" s="4">
-        <v>0.5328565335664905</v>
+        <v>0.4989404297930535</v>
       </c>
       <c r="I13" s="4">
-        <v>0.4526997087860524</v>
+        <v>0.3270348524005177</v>
       </c>
       <c r="J13" s="4">
-        <v>0.5491608004736921</v>
+        <v>0.5133312741235577</v>
       </c>
       <c r="K13" s="4">
         <v>86.24103468547887</v>
@@ -11001,13 +11001,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.2243188219874216</v>
+        <v>0.2142638784441821</v>
       </c>
       <c r="I14" s="4">
-        <v>0.1905732715105103</v>
+        <v>0.1805733323883219</v>
       </c>
       <c r="J14" s="4">
-        <v>0.2689248040853104</v>
+        <v>0.2592958054677302</v>
       </c>
       <c r="K14" s="4">
         <v>95.40102460737397</v>
@@ -11051,13 +11051,13 @@
         <v>0.2469135802469136</v>
       </c>
       <c r="H15" s="4">
-        <v>0.4212777317268163</v>
+        <v>0.4135124206115809</v>
       </c>
       <c r="I15" s="4">
-        <v>0.3269550292195434</v>
+        <v>0.3177123991830956</v>
       </c>
       <c r="J15" s="4">
-        <v>0.5109487197247978</v>
+        <v>0.5069952933612905</v>
       </c>
       <c r="K15" s="4">
         <v>82.9541446208116</v>
@@ -11101,13 +11101,13 @@
         <v>0.2469135802469136</v>
       </c>
       <c r="H16" s="4">
-        <v>0.2422911165110435</v>
+        <v>0.2307693616412596</v>
       </c>
       <c r="I16" s="4">
-        <v>0.2098893273421981</v>
+        <v>0.1978993616519502</v>
       </c>
       <c r="J16" s="4">
-        <v>0.2892985777632439</v>
+        <v>0.2793098102563983</v>
       </c>
       <c r="K16" s="4">
         <v>93.33434114386519</v>
@@ -11151,13 +11151,13 @@
         <v>0.4938271604938271</v>
       </c>
       <c r="H17" s="4">
-        <v>0.3979316776288834</v>
+        <v>0.3831287379159024</v>
       </c>
       <c r="I17" s="4">
-        <v>0.2802495425149321</v>
+        <v>0.2653053586458226</v>
       </c>
       <c r="J17" s="4">
-        <v>0.430408806720342</v>
+        <v>0.4169298263979347</v>
       </c>
       <c r="K17" s="4">
         <v>80.75854539346625</v>
@@ -12040,13 +12040,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="5">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C3" s="5">
         <v>15</v>
       </c>
       <c r="D3" s="5">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E3" s="5">
         <v>2</v>
@@ -12055,7 +12055,7 @@
         <v>27</v>
       </c>
       <c r="G3" s="5">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H3" s="5">
         <v>2</v>
@@ -12084,13 +12084,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="5">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C4" s="5">
         <v>28</v>
       </c>
       <c r="D4" s="5">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E4" s="5">
         <v>6</v>
@@ -12099,7 +12099,7 @@
         <v>51</v>
       </c>
       <c r="G4" s="5">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H4" s="5">
         <v>6</v>
@@ -12304,13 +12304,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="5">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C9" s="5">
         <v>44</v>
       </c>
       <c r="D9" s="5">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E9" s="5">
         <v>2</v>
@@ -12319,7 +12319,7 @@
         <v>56</v>
       </c>
       <c r="G9" s="5">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H9" s="5">
         <v>2</v>
@@ -12392,13 +12392,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="5">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C11" s="5">
         <v>22</v>
       </c>
       <c r="D11" s="5">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E11" s="5">
         <v>0</v>
@@ -12407,7 +12407,7 @@
         <v>39</v>
       </c>
       <c r="G11" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H11" s="5">
         <v>0</v>
@@ -12480,13 +12480,13 @@
         <v>27</v>
       </c>
       <c r="B13" s="5">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="C13" s="5">
         <v>8</v>
       </c>
       <c r="D13" s="5">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="E13" s="5">
         <v>2</v>
@@ -12495,7 +12495,7 @@
         <v>22</v>
       </c>
       <c r="G13" s="5">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="H13" s="5">
         <v>2</v>
@@ -12854,22 +12854,22 @@
         <v>35</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.226596906877781</v>
+        <v>-0.6364090271963505</v>
       </c>
       <c r="O3" s="5">
         <v>102</v>
       </c>
       <c r="P3" s="4">
-        <v>1.435472201043324</v>
+        <v>1.302804116109767</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.8442078956365897</v>
+        <v>0.467343931537049</v>
       </c>
       <c r="R3" s="5">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="S3" s="5">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -12913,16 +12913,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3111132367767277</v>
+        <v>-0.1982574677858793</v>
       </c>
       <c r="O4" s="5">
         <v>50</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4677583199105161</v>
+        <v>0.4659515552406307</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.472593111889402</v>
+        <v>0.468429209276801</v>
       </c>
       <c r="R4" s="5">
         <v>50</v>
@@ -12972,7 +12972,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.428357317535639</v>
+        <v>0.4291183426103089</v>
       </c>
       <c r="O5" s="5">
         <v>35</v>
@@ -12981,7 +12981,7 @@
         <v>0.3583685126535784</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.28029000058592</v>
+        <v>0.2802682570123579</v>
       </c>
       <c r="R5" s="5">
         <v>35</v>
@@ -13031,16 +13031,16 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.1733879157233917</v>
+        <v>-0.6034150250779931</v>
       </c>
       <c r="O6" s="5">
         <v>35</v>
       </c>
       <c r="P6" s="4">
-        <v>0.7094273990331462</v>
+        <v>0.5892372970261931</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.4726523599228055</v>
+        <v>0.3139362632672684</v>
       </c>
       <c r="R6" s="5">
         <v>33</v>
@@ -13090,16 +13090,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.836757801836211</v>
+        <v>-0.8036760338582098</v>
       </c>
       <c r="O7" s="5">
         <v>20</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2663455807340638</v>
+        <v>0.2644034093047429</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2246169618816202</v>
+        <v>0.2191723965115671</v>
       </c>
       <c r="R7" s="5">
         <v>20</v>
@@ -13149,16 +13149,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.7857374800838038</v>
+        <v>-0.7292709127214039</v>
       </c>
       <c r="O8" s="5">
         <v>18</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2976750189885183</v>
+        <v>0.2996980723103098</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.3028598866778653</v>
+        <v>0.2992494202901273</v>
       </c>
       <c r="R8" s="5">
         <v>18</v>
@@ -13208,13 +13208,13 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.3805847845902058</v>
+        <v>-0.3648205667705042</v>
       </c>
       <c r="O9" s="5">
         <v>18</v>
       </c>
       <c r="P9" s="4">
-        <v>0.3420788226482797</v>
+        <v>0.3429085183230008</v>
       </c>
       <c r="Q9" s="4">
         <v>0.3156613713112569</v>
@@ -13267,16 +13267,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.2599036165593134</v>
+        <v>0.2966181834199233</v>
       </c>
       <c r="O10" s="5">
         <v>14</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1827072407003845</v>
+        <v>0.1868290776080411</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.162837831253585</v>
+        <v>0.1599755117427516</v>
       </c>
       <c r="R10" s="5">
         <v>14</v>
@@ -13326,16 +13326,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.563237990156631</v>
+        <v>-0.5788642539409921</v>
       </c>
       <c r="O11" s="5">
         <v>15</v>
       </c>
       <c r="P11" s="4">
-        <v>0.09227037125554703</v>
+        <v>0.09135117926823166</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1013003207293029</v>
+        <v>0.1002585698103455</v>
       </c>
       <c r="R11" s="5">
         <v>15</v>
@@ -13385,13 +13385,13 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.1648963352210038</v>
+        <v>-0.2733554994047154</v>
       </c>
       <c r="O12" s="5">
         <v>14</v>
       </c>
       <c r="P12" s="4">
-        <v>0.8183492288421307</v>
+        <v>0.7992093763391227</v>
       </c>
       <c r="Q12" s="4">
         <v>0.7316298352514943</v>
@@ -13444,13 +13444,13 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.2413175583869815</v>
+        <v>-0.2446382205671398</v>
       </c>
       <c r="O13" s="5">
         <v>16</v>
       </c>
       <c r="P13" s="4">
-        <v>0.5465264965395202</v>
+        <v>0.5463311634700991</v>
       </c>
       <c r="Q13" s="4">
         <v>0.5287134115906156</v>
@@ -13503,16 +13503,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.01836665546385726</v>
+        <v>-0.06803540846158285</v>
       </c>
       <c r="O14" s="5">
         <v>15</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1820259645439971</v>
+        <v>0.1758173704192814</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1660062524142106</v>
+        <v>0.1626950022143622</v>
       </c>
       <c r="R14" s="5">
         <v>15</v>
@@ -13562,16 +13562,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>0.5532431290484965</v>
+        <v>0.5803646855056286</v>
       </c>
       <c r="O15" s="5">
         <v>9</v>
       </c>
       <c r="P15" s="4">
-        <v>0.4843398521054321</v>
+        <v>0.4780810313845555</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.4923342111869715</v>
+        <v>0.4893207049139568</v>
       </c>
       <c r="R15" s="5">
         <v>9</v>
@@ -13744,22 +13744,22 @@
         <v>28</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.657792244208208</v>
+        <v>-1.250885175424628</v>
       </c>
       <c r="O3" s="5">
         <v>78</v>
       </c>
       <c r="P3" s="4">
-        <v>1.063763635119781</v>
+        <v>1.024935367337061</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.8682928487230103</v>
+        <v>0.6638413378711903</v>
       </c>
       <c r="R3" s="5">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="S3" s="5">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -13803,16 +13803,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.6198353283700271</v>
+        <v>-0.6652435960422736</v>
       </c>
       <c r="O4" s="5">
         <v>40</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3628706891620123</v>
+        <v>0.3630355788623442</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2908026968120612</v>
+        <v>0.2882142681199184</v>
       </c>
       <c r="R4" s="5">
         <v>40</v>
@@ -13862,7 +13862,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1539181443958488</v>
+        <v>0.1534460756083718</v>
       </c>
       <c r="O5" s="5">
         <v>34</v>
@@ -13921,16 +13921,16 @@
         <v>1</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.1514090320393514</v>
+        <v>-0.3210884194850223</v>
       </c>
       <c r="O6" s="5">
         <v>33</v>
       </c>
       <c r="P6" s="4">
-        <v>0.6727738637259653</v>
+        <v>0.6489948683538387</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.4850907979296222</v>
+        <v>0.4447620919991095</v>
       </c>
       <c r="R6" s="5">
         <v>32</v>
@@ -13980,16 +13980,16 @@
         <v>5</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.750111165372073</v>
+        <v>-1.647746885180823</v>
       </c>
       <c r="O7" s="5">
         <v>20</v>
       </c>
       <c r="P7" s="4">
-        <v>0.4168125159596622</v>
+        <v>0.4034245813950706</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.4317365934947156</v>
+        <v>0.4170098654736648</v>
       </c>
       <c r="R7" s="5">
         <v>20</v>
@@ -14039,16 +14039,16 @@
         <v>5</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.651931745410871</v>
+        <v>-1.487943963293219</v>
       </c>
       <c r="O8" s="5">
         <v>18</v>
       </c>
       <c r="P8" s="4">
-        <v>0.5410813034435726</v>
+        <v>0.5506357433762223</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.49377382828683</v>
+        <v>0.4775893778553129</v>
       </c>
       <c r="R8" s="5">
         <v>18</v>
@@ -14098,16 +14098,16 @@
         <v>1</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.8957107540099012</v>
+        <v>-1.044453269540099</v>
       </c>
       <c r="O9" s="5">
         <v>19</v>
       </c>
       <c r="P9" s="4">
-        <v>0.5692108162420633</v>
+        <v>0.5489871460618145</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.5692108162420633</v>
+        <v>0.5489871460618145</v>
       </c>
       <c r="R9" s="5">
         <v>19</v>
@@ -14157,16 +14157,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.219775274921796</v>
+        <v>0.1861768470407696</v>
       </c>
       <c r="O10" s="5">
         <v>11</v>
       </c>
       <c r="P10" s="4">
-        <v>0.611894896681046</v>
+        <v>0.5980602499065057</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.4140615584839891</v>
+        <v>0.4110071559493504</v>
       </c>
       <c r="R10" s="5">
         <v>11</v>
@@ -14216,13 +14216,13 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.7866794617096146</v>
+        <v>-0.8275241450537578</v>
       </c>
       <c r="O11" s="5">
         <v>14</v>
       </c>
       <c r="P11" s="4">
-        <v>0.2472722923164593</v>
+        <v>0.2400644070204341</v>
       </c>
       <c r="Q11" s="4">
         <v>0.230967673790084</v>
@@ -14275,22 +14275,22 @@
         <v>2</v>
       </c>
       <c r="N12" s="4">
-        <v>-1.334679131247478</v>
+        <v>-1.1062966808895</v>
       </c>
       <c r="O12" s="5">
         <v>14</v>
       </c>
       <c r="P12" s="4">
-        <v>0.703368757895261</v>
+        <v>0.7219163589372115</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.5800097434034889</v>
+        <v>0.4394616549504393</v>
       </c>
       <c r="R12" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S12" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="25" customHeight="1">
@@ -14334,16 +14334,16 @@
         <v>2</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.9612964449725041</v>
+        <v>-1.087391647728509</v>
       </c>
       <c r="O13" s="5">
         <v>16</v>
       </c>
       <c r="P13" s="4">
-        <v>0.7998050034605458</v>
+        <v>0.7895256108535892</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.827540842739495</v>
+        <v>0.8244999382668539</v>
       </c>
       <c r="R13" s="5">
         <v>16</v>
@@ -14393,16 +14393,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.476813934956486</v>
+        <v>-0.5511276905963314</v>
       </c>
       <c r="O14" s="5">
         <v>14</v>
       </c>
       <c r="P14" s="4">
-        <v>0.3749039456231133</v>
+        <v>0.3833828473962058</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.3686637732030156</v>
+        <v>0.3677376958522863</v>
       </c>
       <c r="R14" s="5">
         <v>14</v>
@@ -14452,16 +14452,16 @@
         <v>1</v>
       </c>
       <c r="N15" s="4">
-        <v>-0.9349072098622047</v>
+        <v>-0.6598055342328735</v>
       </c>
       <c r="O15" s="5">
         <v>9</v>
       </c>
       <c r="P15" s="4">
-        <v>0.6752556351391086</v>
+        <v>0.6319308755158161</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.612270378366107</v>
+        <v>0.5817035255184035</v>
       </c>
       <c r="R15" s="5">
         <v>9</v>
@@ -14634,16 +14634,16 @@
         <v>6</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5607934697101579</v>
+        <v>-0.3005507876951015</v>
       </c>
       <c r="O3" s="5">
         <v>96</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7985022536753318</v>
+        <v>0.7779824310231274</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.674842266859577</v>
+        <v>0.6582996222650956</v>
       </c>
       <c r="R3" s="5">
         <v>94</v>
@@ -14693,16 +14693,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.03617028378160588</v>
+        <v>0.02559841577385669</v>
       </c>
       <c r="O4" s="5">
         <v>48</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2240992772598743</v>
+        <v>0.2153961182309733</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2028235189778229</v>
+        <v>0.1985424883261354</v>
       </c>
       <c r="R4" s="5">
         <v>48</v>
@@ -14752,7 +14752,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3661961875609689</v>
+        <v>0.3661958101292839</v>
       </c>
       <c r="O5" s="5">
         <v>38</v>
@@ -14811,16 +14811,16 @@
         <v>1</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.09070567039816524</v>
+        <v>-0.3183891404041788</v>
       </c>
       <c r="O6" s="5">
         <v>36</v>
       </c>
       <c r="P6" s="4">
-        <v>0.5435534644759172</v>
+        <v>0.4695709878946218</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.3228443528451732</v>
+        <v>0.2275724656547287</v>
       </c>
       <c r="R6" s="5">
         <v>35</v>
@@ -14870,7 +14870,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.25540225527718</v>
+        <v>-0.2659171228006016</v>
       </c>
       <c r="O7" s="5">
         <v>19</v>
@@ -14879,7 +14879,7 @@
         <v>0.2269216929840199</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2165113302235365</v>
+        <v>0.2159579161433564</v>
       </c>
       <c r="R7" s="5">
         <v>19</v>
@@ -14929,16 +14929,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.2299581595510799</v>
+        <v>-0.1441608541354071</v>
       </c>
       <c r="O8" s="5">
         <v>21</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2405196085834639</v>
+        <v>0.2209432425775698</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2405196085834639</v>
+        <v>0.2209432425775698</v>
       </c>
       <c r="R8" s="5">
         <v>21</v>
@@ -14988,16 +14988,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.2746698781605422</v>
+        <v>-0.2826570093602641</v>
       </c>
       <c r="O9" s="5">
         <v>18</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2663967354277255</v>
+        <v>0.2665604567905814</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2724297736335925</v>
+        <v>0.2721588611166226</v>
       </c>
       <c r="R9" s="5">
         <v>18</v>
@@ -15047,13 +15047,13 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.3254985187361724</v>
+        <v>0.3409506497846451</v>
       </c>
       <c r="O10" s="5">
         <v>14</v>
       </c>
       <c r="P10" s="4">
-        <v>0.2933969251938864</v>
+        <v>0.2961237718494992</v>
       </c>
       <c r="Q10" s="4">
         <v>0.2105103083319721</v>
@@ -15106,16 +15106,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.1767635654869082</v>
+        <v>-0.1349918276246171</v>
       </c>
       <c r="O11" s="5">
         <v>16</v>
       </c>
       <c r="P11" s="4">
-        <v>0.1155576924025167</v>
+        <v>0.1098152138010311</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1034804300065844</v>
+        <v>0.09476831287611276</v>
       </c>
       <c r="R11" s="5">
         <v>16</v>
@@ -15165,16 +15165,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>0.007573892434265872</v>
+        <v>-0.09944909695332171</v>
       </c>
       <c r="O12" s="5">
         <v>16</v>
       </c>
       <c r="P12" s="4">
-        <v>0.4074836051556892</v>
+        <v>0.3706947980069398</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.4151466453755575</v>
+        <v>0.3827474746167354</v>
       </c>
       <c r="R12" s="5">
         <v>16</v>
@@ -15224,16 +15224,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.129908108680598</v>
+        <v>-0.002053689182503149</v>
       </c>
       <c r="O13" s="5">
         <v>17</v>
       </c>
       <c r="P13" s="4">
-        <v>0.2714702291276175</v>
+        <v>0.2574787035127348</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.2714702291276175</v>
+        <v>0.2574787035127348</v>
       </c>
       <c r="R13" s="5">
         <v>17</v>
@@ -15283,16 +15283,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.08312399809074122</v>
+        <v>0.09939000090525951</v>
       </c>
       <c r="O14" s="5">
         <v>15</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1081208854893703</v>
+        <v>0.1061511476627857</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1055753493235291</v>
+        <v>0.1023898954542043</v>
       </c>
       <c r="R14" s="5">
         <v>15</v>
@@ -15342,16 +15342,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>0.785369232614847</v>
+        <v>0.8884743875532877</v>
       </c>
       <c r="O15" s="5">
         <v>13</v>
       </c>
       <c r="P15" s="4">
-        <v>0.3199425451350729</v>
+        <v>0.2974095945895757</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.3199425451350729</v>
+        <v>0.2974095945895757</v>
       </c>
       <c r="R15" s="5">
         <v>13</v>
@@ -15524,16 +15524,16 @@
         <v>19</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.860588943358777</v>
+        <v>-0.78862599695276</v>
       </c>
       <c r="O3" s="5">
         <v>87</v>
       </c>
       <c r="P3" s="4">
-        <v>0.9189398458629132</v>
+        <v>0.914793985057035</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6845248710657741</v>
+        <v>0.683267706019297</v>
       </c>
       <c r="R3" s="5">
         <v>79</v>
@@ -15583,16 +15583,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2581875970078657</v>
+        <v>-0.3399900864860683</v>
       </c>
       <c r="O4" s="5">
         <v>52</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3675060746723592</v>
+        <v>0.3642920514233153</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3675060746723592</v>
+        <v>0.3642920514233153</v>
       </c>
       <c r="R4" s="5">
         <v>52</v>
@@ -15642,7 +15642,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4113602100429229</v>
+        <v>0.4113472673197975</v>
       </c>
       <c r="O5" s="5">
         <v>28</v>
@@ -15701,16 +15701,16 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.07650426775174257</v>
+        <v>-0.5160967498959508</v>
       </c>
       <c r="O6" s="5">
         <v>34</v>
       </c>
       <c r="P6" s="4">
-        <v>0.7811862225555696</v>
+        <v>0.6340293198027211</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.5427018653670477</v>
+        <v>0.3670962165028868</v>
       </c>
       <c r="R6" s="5">
         <v>32</v>
@@ -15760,16 +15760,16 @@
         <v>1</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.083528755968291</v>
+        <v>-1.024831053800881</v>
       </c>
       <c r="O7" s="5">
         <v>20</v>
       </c>
       <c r="P7" s="4">
-        <v>0.4324594804731366</v>
+        <v>0.4351850448398512</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.372051876838741</v>
+        <v>0.369180227425386</v>
       </c>
       <c r="R7" s="5">
         <v>20</v>
@@ -15819,16 +15819,16 @@
         <v>2</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.191772007029565</v>
+        <v>-1.005783728935057</v>
       </c>
       <c r="O8" s="5">
         <v>19</v>
       </c>
       <c r="P8" s="4">
-        <v>0.5182217851099978</v>
+        <v>0.5021773218787053</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.5047329622140242</v>
+        <v>0.4674218946326475</v>
       </c>
       <c r="R8" s="5">
         <v>19</v>
@@ -15878,16 +15878,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.5688956454153716</v>
+        <v>-0.6584037074353546</v>
       </c>
       <c r="O9" s="5">
         <v>18</v>
       </c>
       <c r="P9" s="4">
-        <v>0.4965408687411374</v>
+        <v>0.4960074438430112</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.5123536336964375</v>
+        <v>0.5068179039695274</v>
       </c>
       <c r="R9" s="5">
         <v>18</v>
@@ -15937,16 +15937,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.06410750518261921</v>
+        <v>-0.02811438052594895</v>
       </c>
       <c r="O10" s="5">
         <v>14</v>
       </c>
       <c r="P10" s="4">
-        <v>0.2801532844151713</v>
+        <v>0.2747591568935177</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.2804675654084089</v>
+        <v>0.276488490893306</v>
       </c>
       <c r="R10" s="5">
         <v>14</v>
@@ -15996,16 +15996,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.494580248760758</v>
+        <v>-0.4977971791813616</v>
       </c>
       <c r="O11" s="5">
         <v>15</v>
       </c>
       <c r="P11" s="4">
-        <v>0.2260424044046564</v>
+        <v>0.2258531732034445</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.2264845363729789</v>
+        <v>0.2262700743449386</v>
       </c>
       <c r="R11" s="5">
         <v>15</v>
@@ -16055,16 +16055,16 @@
         <v>2</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.5822928779971335</v>
+        <v>-0.5428107492043637</v>
       </c>
       <c r="O12" s="5">
         <v>16</v>
       </c>
       <c r="P12" s="4">
-        <v>0.6782643453094245</v>
+        <v>0.680586823473705</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.538720511536485</v>
+        <v>0.536088369616967</v>
       </c>
       <c r="R12" s="5">
         <v>15</v>
@@ -16114,16 +16114,16 @@
         <v>2</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.8306163607439885</v>
+        <v>-0.9400534335509292</v>
       </c>
       <c r="O13" s="5">
         <v>16</v>
       </c>
       <c r="P13" s="4">
-        <v>0.6891662049041877</v>
+        <v>0.6684419113765162</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.7099234615127443</v>
+        <v>0.6947437166900272</v>
       </c>
       <c r="R13" s="5">
         <v>16</v>
@@ -16173,16 +16173,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.1293573277488273</v>
+        <v>-0.1802088539989199</v>
       </c>
       <c r="O14" s="5">
         <v>15</v>
       </c>
       <c r="P14" s="4">
-        <v>0.2600851700183436</v>
+        <v>0.253728729237082</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.2698010264024034</v>
+        <v>0.2664109246523973</v>
       </c>
       <c r="R14" s="5">
         <v>15</v>
@@ -16232,13 +16232,13 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>-0.07821009174949722</v>
+        <v>-0.06689429903053679</v>
       </c>
       <c r="O15" s="5">
         <v>8</v>
       </c>
       <c r="P15" s="4">
-        <v>0.6327188035530316</v>
+        <v>0.6335892491467978</v>
       </c>
       <c r="Q15" s="4">
         <v>0.6541591306886403</v>
@@ -16414,16 +16414,16 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3247595769592971</v>
+        <v>-0.09811497514601797</v>
       </c>
       <c r="O3" s="5">
         <v>105</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6349509677919066</v>
+        <v>0.6022689337143929</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5967559906458231</v>
+        <v>0.5629965761509437</v>
       </c>
       <c r="R3" s="5">
         <v>103</v>
@@ -16473,16 +16473,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1084156646988413</v>
+        <v>0.1281480434226978</v>
       </c>
       <c r="O4" s="5">
         <v>50</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1651096690231162</v>
+        <v>0.162938939677238</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1543574855566723</v>
+        <v>0.1528892221859132</v>
       </c>
       <c r="R4" s="5">
         <v>50</v>
@@ -16532,7 +16532,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2358711429086198</v>
+        <v>0.2358797761698952</v>
       </c>
       <c r="O5" s="5">
         <v>38</v>
@@ -16591,16 +16591,16 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.09298532714839032</v>
+        <v>-0.3145307292143116</v>
       </c>
       <c r="O6" s="5">
         <v>38</v>
       </c>
       <c r="P6" s="4">
-        <v>0.4186925845208622</v>
+        <v>0.3403373186225508</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2381748953400682</v>
+        <v>0.1388054108938377</v>
       </c>
       <c r="R6" s="5">
         <v>36</v>
@@ -16650,7 +16650,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.4306443818627899</v>
+        <v>0.4396383391722338</v>
       </c>
       <c r="O7" s="5">
         <v>22</v>
@@ -16709,16 +16709,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.2626689310903506</v>
+        <v>0.3346974246087484</v>
       </c>
       <c r="O8" s="5">
         <v>21</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1553855717694017</v>
+        <v>0.1519556435066209</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1553855717694017</v>
+        <v>0.1519556435066209</v>
       </c>
       <c r="R8" s="5">
         <v>21</v>
@@ -16768,16 +16768,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.07111414820706398</v>
+        <v>-0.001783413114026189</v>
       </c>
       <c r="O9" s="5">
         <v>19</v>
       </c>
       <c r="P9" s="4">
-        <v>0.1594098989354025</v>
+        <v>0.1434370787518626</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1594098989354025</v>
+        <v>0.1434370787518626</v>
       </c>
       <c r="R9" s="5">
         <v>19</v>
@@ -16827,16 +16827,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.1504789837799763</v>
+        <v>0.1206844421103597</v>
       </c>
       <c r="O10" s="5">
         <v>16</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1083499309717059</v>
+        <v>0.09964441519953064</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1031964773608252</v>
+        <v>0.09580902570723993</v>
       </c>
       <c r="R10" s="5">
         <v>16</v>
@@ -16886,16 +16886,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.05502198458179919</v>
+        <v>-0.02855780145182507</v>
       </c>
       <c r="O11" s="5">
         <v>16</v>
       </c>
       <c r="P11" s="4">
-        <v>0.09428477752552521</v>
+        <v>0.09199684644879787</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.07489267667438071</v>
+        <v>0.07080773845973454</v>
       </c>
       <c r="R11" s="5">
         <v>16</v>
@@ -16945,16 +16945,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>0.3720484381201459</v>
+        <v>0.2742222010710975</v>
       </c>
       <c r="O12" s="5">
         <v>16</v>
       </c>
       <c r="P12" s="4">
-        <v>0.3641257336536428</v>
+        <v>0.3446018274698872</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.2971807667012172</v>
+        <v>0.2825507561965424</v>
       </c>
       <c r="R12" s="5">
         <v>16</v>
@@ -17004,16 +17004,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.2897513533646227</v>
+        <v>0.3164178451988846</v>
       </c>
       <c r="O13" s="5">
         <v>17</v>
       </c>
       <c r="P13" s="4">
-        <v>0.167752893324168</v>
+        <v>0.1634924223925576</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.167752893324168</v>
+        <v>0.1634924223925576</v>
       </c>
       <c r="R13" s="5">
         <v>17</v>
@@ -17063,16 +17063,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.1973942703780267</v>
+        <v>0.2196390744429664</v>
       </c>
       <c r="O14" s="5">
         <v>16</v>
       </c>
       <c r="P14" s="4">
-        <v>0.07254536156222002</v>
+        <v>0.07062914062862546</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.07254536156222002</v>
+        <v>0.07062914062862546</v>
       </c>
       <c r="R14" s="5">
         <v>16</v>
@@ -17122,16 +17122,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>0.5874685143935494</v>
+        <v>0.5056020490883384</v>
       </c>
       <c r="O15" s="5">
         <v>13</v>
       </c>
       <c r="P15" s="4">
-        <v>0.2667721241909581</v>
+        <v>0.2534134016851357</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.2667721241909581</v>
+        <v>0.2534134016851357</v>
       </c>
       <c r="R15" s="5">
         <v>13</v>
